--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_9_10.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_9_10.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-32515.39935937516</v>
+        <v>-44279.89839730911</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9575967.955179952</v>
+        <v>10095312.09622575</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22123045.90398397</v>
+        <v>22050385.14120355</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4279495.778663328</v>
+        <v>4277222.024852714</v>
       </c>
     </row>
     <row r="11">
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>91.99244221512851</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K11" t="n">
-        <v>86.62179576859864</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L11" t="n">
-        <v>70.18749034687164</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M11" t="n">
-        <v>46.10777594084058</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N11" t="n">
-        <v>42.19343545588742</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O11" t="n">
-        <v>53.31202549203849</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P11" t="n">
-        <v>80.3500761572796</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q11" t="n">
-        <v>108.9989009297259</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,13 +8746,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>73.79799459119499</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K12" t="n">
-        <v>47.18825972907598</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L12" t="n">
-        <v>16.65999298742136</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -8761,13 +8761,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>9.025801048218028</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>26.77235081055666</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q12" t="n">
-        <v>68.3200382369649</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>74.33161882627311</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L13" t="n">
-        <v>64.91100415009075</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M13" t="n">
-        <v>65.14835771809689</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N13" t="n">
-        <v>55.66238053080693</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O13" t="n">
-        <v>71.93148927151492</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P13" t="n">
-        <v>80.80433191800012</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>91.99244221512851</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K14" t="n">
-        <v>86.62179576859867</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L14" t="n">
-        <v>70.18749034687167</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M14" t="n">
-        <v>46.10777594084061</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N14" t="n">
-        <v>42.19343545588742</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O14" t="n">
-        <v>53.31202549203852</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P14" t="n">
-        <v>80.35007615727963</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q14" t="n">
-        <v>108.9989009297259</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,13 +8983,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>73.79799459119499</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K15" t="n">
-        <v>47.18825972907598</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L15" t="n">
-        <v>16.65999298742136</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -8998,13 +8998,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>9.025801048218057</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>26.77235081055667</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q15" t="n">
-        <v>68.32003823696492</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>74.33161882627311</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L16" t="n">
-        <v>64.91100415009076</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M16" t="n">
-        <v>65.14835771809689</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N16" t="n">
-        <v>55.66238053080694</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O16" t="n">
-        <v>71.93148927151492</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P16" t="n">
-        <v>80.80433191800012</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>91.99244221512851</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K17" t="n">
-        <v>86.62179576859867</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L17" t="n">
-        <v>70.18749034687167</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M17" t="n">
-        <v>46.10777594084061</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N17" t="n">
-        <v>42.19343545588742</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O17" t="n">
-        <v>53.31202549203852</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P17" t="n">
-        <v>80.35007615727963</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q17" t="n">
-        <v>108.9989009297259</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,13 +9220,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>73.79799459119499</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K18" t="n">
-        <v>47.18825972907598</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L18" t="n">
-        <v>16.65999298742136</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -9235,13 +9235,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>9.025801048218057</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>26.77235081055667</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q18" t="n">
-        <v>68.32003823696492</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>74.33161882627311</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L19" t="n">
-        <v>64.91100415009076</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M19" t="n">
-        <v>65.14835771809689</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N19" t="n">
-        <v>55.66238053080694</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O19" t="n">
-        <v>71.93148927151492</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P19" t="n">
-        <v>80.80433191800012</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>91.99244221512851</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K20" t="n">
-        <v>86.62179576859867</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L20" t="n">
-        <v>70.18749034687167</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M20" t="n">
-        <v>46.10777594084061</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N20" t="n">
-        <v>42.19343545588742</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O20" t="n">
-        <v>53.31202549203852</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P20" t="n">
-        <v>80.35007615727963</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q20" t="n">
-        <v>108.9989009297259</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,13 +9457,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>73.79799459119499</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K21" t="n">
-        <v>47.18825972907598</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L21" t="n">
-        <v>16.65999298742136</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9472,13 +9472,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>9.025801048218057</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>26.77235081055667</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q21" t="n">
-        <v>68.32003823696492</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>74.33161882627311</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L22" t="n">
-        <v>64.91100415009076</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M22" t="n">
-        <v>65.14835771809689</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N22" t="n">
-        <v>55.66238053080694</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O22" t="n">
-        <v>71.93148927151492</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P22" t="n">
-        <v>80.80433191800012</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>91.99244221512851</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K23" t="n">
-        <v>86.62179576859867</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L23" t="n">
-        <v>70.18749034687167</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M23" t="n">
-        <v>46.10777594084061</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N23" t="n">
-        <v>42.19343545588742</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O23" t="n">
-        <v>53.31202549203852</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P23" t="n">
-        <v>80.35007615727963</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q23" t="n">
-        <v>108.9989009297259</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,13 +9694,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>73.79799459119499</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K24" t="n">
-        <v>47.18825972907598</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L24" t="n">
-        <v>16.65999298742136</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -9709,13 +9709,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>9.025801048218057</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>26.77235081055667</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q24" t="n">
-        <v>68.32003823696492</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>74.33161882627311</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L25" t="n">
-        <v>64.91100415009076</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M25" t="n">
-        <v>65.14835771809689</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N25" t="n">
-        <v>55.66238053080694</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O25" t="n">
-        <v>71.93148927151492</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P25" t="n">
-        <v>80.80433191800012</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>91.99244221512851</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K26" t="n">
-        <v>86.62179576859867</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L26" t="n">
-        <v>70.18749034687167</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M26" t="n">
-        <v>46.10777594084061</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N26" t="n">
-        <v>42.19343545588742</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O26" t="n">
-        <v>53.31202549203852</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P26" t="n">
-        <v>80.35007615727963</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q26" t="n">
-        <v>108.9989009297259</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,13 +9931,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>73.79799459119499</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K27" t="n">
-        <v>47.18825972907598</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L27" t="n">
-        <v>16.65999298742136</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -9946,13 +9946,13 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>9.025801048218057</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>26.77235081055667</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q27" t="n">
-        <v>68.32003823696492</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>74.33161882627311</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L28" t="n">
-        <v>64.91100415009076</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M28" t="n">
-        <v>65.14835771809689</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N28" t="n">
-        <v>55.66238053080694</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O28" t="n">
-        <v>71.93148927151492</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P28" t="n">
-        <v>80.80433191800012</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>91.99244221512851</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K29" t="n">
-        <v>86.62179576859867</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L29" t="n">
-        <v>70.18749034687167</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M29" t="n">
-        <v>46.10777594084061</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N29" t="n">
-        <v>42.19343545588742</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O29" t="n">
-        <v>53.31202549203852</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P29" t="n">
-        <v>80.35007615727963</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q29" t="n">
-        <v>108.9989009297259</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,13 +10168,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>73.79799459119499</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K30" t="n">
-        <v>47.18825972907598</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L30" t="n">
-        <v>16.65999298742136</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -10183,13 +10183,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>9.025801048218057</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>26.77235081055667</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q30" t="n">
-        <v>68.32003823696492</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>74.33161882627311</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L31" t="n">
-        <v>64.91100415009076</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M31" t="n">
-        <v>65.14835771809689</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N31" t="n">
-        <v>55.66238053080694</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O31" t="n">
-        <v>71.93148927151492</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P31" t="n">
-        <v>80.80433191800012</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>91.99244221512851</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K32" t="n">
-        <v>86.62179576859867</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L32" t="n">
-        <v>70.18749034687167</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M32" t="n">
-        <v>46.10777594084061</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N32" t="n">
-        <v>42.19343545588742</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O32" t="n">
-        <v>53.31202549203852</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P32" t="n">
-        <v>80.35007615727963</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q32" t="n">
-        <v>108.9989009297259</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,13 +10405,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>73.79799459119499</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K33" t="n">
-        <v>47.18825972907598</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L33" t="n">
-        <v>16.65999298742136</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -10420,13 +10420,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>9.025801048218057</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>26.77235081055667</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q33" t="n">
-        <v>68.32003823696492</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>74.33161882627311</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L34" t="n">
-        <v>64.91100415009076</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M34" t="n">
-        <v>65.14835771809689</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N34" t="n">
-        <v>55.66238053080694</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O34" t="n">
-        <v>71.93148927151492</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P34" t="n">
-        <v>80.80433191800012</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>91.99244221512851</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K35" t="n">
-        <v>86.62179576859867</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L35" t="n">
-        <v>70.18749034687167</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M35" t="n">
-        <v>46.10777594084061</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N35" t="n">
-        <v>42.19343545588742</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O35" t="n">
-        <v>53.31202549203852</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P35" t="n">
-        <v>80.35007615727963</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q35" t="n">
-        <v>108.9989009297259</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,13 +10642,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>73.79799459119499</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K36" t="n">
-        <v>47.18825972907598</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L36" t="n">
-        <v>16.65999298742136</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -10657,13 +10657,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>9.025801048218057</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>26.77235081055667</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q36" t="n">
-        <v>68.32003823696492</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>74.33161882627311</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L37" t="n">
-        <v>64.91100415009076</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M37" t="n">
-        <v>65.14835771809689</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N37" t="n">
-        <v>55.66238053080694</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O37" t="n">
-        <v>71.93148927151492</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P37" t="n">
-        <v>80.80433191800012</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>91.99244221512851</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K38" t="n">
-        <v>86.62179576859867</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L38" t="n">
-        <v>70.18749034687167</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M38" t="n">
-        <v>46.10777594084061</v>
+        <v>20.92686739226639</v>
       </c>
       <c r="N38" t="n">
-        <v>42.19343545588742</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O38" t="n">
-        <v>53.31202549203852</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P38" t="n">
-        <v>80.35007615727963</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q38" t="n">
-        <v>108.9989009297259</v>
+        <v>93.51262335026311</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,13 +10879,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>73.79799459119499</v>
+        <v>66.54876907979123</v>
       </c>
       <c r="K39" t="n">
-        <v>47.18825972907598</v>
+        <v>34.79817869043561</v>
       </c>
       <c r="L39" t="n">
-        <v>16.65999298742136</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -10894,13 +10894,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>9.025801048218057</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>26.77235081055667</v>
+        <v>12.12044141380177</v>
       </c>
       <c r="Q39" t="n">
-        <v>68.32003823696492</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>74.33161882627311</v>
+        <v>66.8579709251007</v>
       </c>
       <c r="L40" t="n">
-        <v>64.91100415009076</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M40" t="n">
-        <v>65.14835771809689</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N40" t="n">
-        <v>55.66238053080694</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O40" t="n">
-        <v>71.93148927151492</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P40" t="n">
-        <v>80.80433191800012</v>
+        <v>73.02425275703003</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>91.99244221512851</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K41" t="n">
-        <v>86.62179576859867</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L41" t="n">
-        <v>70.18749034687167</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M41" t="n">
-        <v>46.10777594084061</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N41" t="n">
-        <v>42.19343545588742</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O41" t="n">
-        <v>53.31202549203852</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P41" t="n">
-        <v>80.35007615727963</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q41" t="n">
-        <v>108.9989009297259</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,13 +11116,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>73.79799459119499</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K42" t="n">
-        <v>47.18825972907598</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L42" t="n">
-        <v>16.65999298742136</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -11131,13 +11131,13 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>9.025801048218057</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>26.77235081055667</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q42" t="n">
-        <v>68.32003823696492</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>74.33161882627311</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L43" t="n">
-        <v>64.91100415009076</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M43" t="n">
-        <v>65.14835771809689</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N43" t="n">
-        <v>55.66238053080694</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O43" t="n">
-        <v>71.93148927151492</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P43" t="n">
-        <v>80.80433191800012</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>91.99244221512851</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K44" t="n">
-        <v>86.62179576859867</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L44" t="n">
-        <v>70.18749034687167</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M44" t="n">
-        <v>46.10777594084061</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N44" t="n">
-        <v>42.19343545588742</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O44" t="n">
-        <v>53.31202549203852</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P44" t="n">
-        <v>80.35007615727963</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q44" t="n">
-        <v>108.9989009297259</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,13 +11353,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>73.79799459119499</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K45" t="n">
-        <v>47.18825972907598</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L45" t="n">
-        <v>16.65999298742136</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -11368,13 +11368,13 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>9.025801048218057</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>26.77235081055667</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q45" t="n">
-        <v>68.32003823696492</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>74.33161882627311</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L46" t="n">
-        <v>64.91100415009076</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M46" t="n">
-        <v>65.14835771809689</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N46" t="n">
-        <v>55.66238053080694</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O46" t="n">
-        <v>71.93148927151492</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P46" t="n">
-        <v>80.80433191800012</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.2534912839793</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H11" t="n">
-        <v>328.729209150943</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I11" t="n">
-        <v>170.0248242437727</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>83.95940437331049</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S11" t="n">
-        <v>185.110371093783</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T11" t="n">
-        <v>218.5027741872469</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U11" t="n">
-        <v>251.261713209344</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H12" t="n">
-        <v>106.8135385761191</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I12" t="n">
-        <v>70.06785926650942</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>65.30202283188841</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S12" t="n">
-        <v>161.2554824245925</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T12" t="n">
-        <v>197.9019079401046</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9044481187107</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.5203236207538</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H13" t="n">
-        <v>158.0426151303904</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I13" t="n">
-        <v>141.296573287914</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J13" t="n">
-        <v>60.08381946093508</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>46.75104325169439</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R13" t="n">
-        <v>156.1309979345465</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S13" t="n">
-        <v>215.8143521353329</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T13" t="n">
-        <v>225.9346058217241</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.2534912839793</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H14" t="n">
-        <v>328.729209150943</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I14" t="n">
-        <v>170.0248242437727</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>83.95940437331049</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S14" t="n">
-        <v>185.110371093783</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T14" t="n">
-        <v>218.5027741872469</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U14" t="n">
-        <v>251.261713209344</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H15" t="n">
-        <v>106.8135385761191</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I15" t="n">
-        <v>70.06785926650942</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>65.30202283188841</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S15" t="n">
-        <v>161.2554824245925</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T15" t="n">
-        <v>197.9019079401046</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9044481187107</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.5203236207538</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H16" t="n">
-        <v>158.0426151303904</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I16" t="n">
-        <v>141.296573287914</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J16" t="n">
-        <v>60.08381946093508</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>46.7510432516944</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R16" t="n">
-        <v>156.1309979345465</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S16" t="n">
-        <v>215.8143521353329</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T16" t="n">
-        <v>225.9346058217241</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.2534912839793</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H17" t="n">
-        <v>328.729209150943</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I17" t="n">
-        <v>170.0248242437727</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>83.95940437331049</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S17" t="n">
-        <v>185.110371093783</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T17" t="n">
-        <v>218.5027741872469</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U17" t="n">
-        <v>251.261713209344</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H18" t="n">
-        <v>106.8135385761191</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I18" t="n">
-        <v>70.06785926650942</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>65.30202283188841</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S18" t="n">
-        <v>161.2554824245925</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T18" t="n">
-        <v>197.9019079401046</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9044481187107</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.5203236207538</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H19" t="n">
-        <v>158.0426151303904</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I19" t="n">
-        <v>141.296573287914</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J19" t="n">
-        <v>60.08381946093508</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>46.7510432516944</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R19" t="n">
-        <v>156.1309979345465</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S19" t="n">
-        <v>215.8143521353329</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T19" t="n">
-        <v>225.9346058217241</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.2534912839793</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H20" t="n">
-        <v>328.729209150943</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I20" t="n">
-        <v>170.0248242437727</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>83.95940437331049</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S20" t="n">
-        <v>185.110371093783</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T20" t="n">
-        <v>218.5027741872469</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U20" t="n">
-        <v>251.261713209344</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H21" t="n">
-        <v>106.8135385761191</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I21" t="n">
-        <v>70.06785926650942</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>65.30202283188841</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S21" t="n">
-        <v>161.2554824245925</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T21" t="n">
-        <v>197.9019079401046</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9044481187107</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.5203236207538</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H22" t="n">
-        <v>158.0426151303904</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I22" t="n">
-        <v>141.296573287914</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J22" t="n">
-        <v>60.08381946093508</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>46.7510432516944</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R22" t="n">
-        <v>156.1309979345465</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S22" t="n">
-        <v>215.8143521353329</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T22" t="n">
-        <v>225.9346058217241</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.2534912839793</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H23" t="n">
-        <v>328.729209150943</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I23" t="n">
-        <v>170.0248242437727</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>83.95940437331049</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S23" t="n">
-        <v>185.110371093783</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T23" t="n">
-        <v>218.5027741872469</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U23" t="n">
-        <v>251.261713209344</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H24" t="n">
-        <v>106.8135385761191</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I24" t="n">
-        <v>70.06785926650942</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>65.30202283188841</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S24" t="n">
-        <v>161.2554824245925</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T24" t="n">
-        <v>197.9019079401046</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9044481187107</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.5203236207538</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H25" t="n">
-        <v>158.0426151303904</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I25" t="n">
-        <v>141.296573287914</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J25" t="n">
-        <v>60.08381946093508</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>46.7510432516944</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R25" t="n">
-        <v>156.1309979345465</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S25" t="n">
-        <v>215.8143521353329</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T25" t="n">
-        <v>225.9346058217241</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.2534912839793</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H26" t="n">
-        <v>328.729209150943</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I26" t="n">
-        <v>170.0248242437727</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>83.95940437331049</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S26" t="n">
-        <v>185.110371093783</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T26" t="n">
-        <v>218.5027741872469</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U26" t="n">
-        <v>251.261713209344</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H27" t="n">
-        <v>106.8135385761191</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I27" t="n">
-        <v>70.06785926650942</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>65.30202283188841</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S27" t="n">
-        <v>161.2554824245925</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T27" t="n">
-        <v>197.9019079401046</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9044481187107</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.5203236207538</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H28" t="n">
-        <v>158.0426151303904</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I28" t="n">
-        <v>141.296573287914</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J28" t="n">
-        <v>60.08381946093508</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>46.7510432516944</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R28" t="n">
-        <v>156.1309979345465</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S28" t="n">
-        <v>215.8143521353329</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T28" t="n">
-        <v>225.9346058217241</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.2534912839793</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H29" t="n">
-        <v>328.729209150943</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I29" t="n">
-        <v>170.0248242437727</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>83.95940437331049</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S29" t="n">
-        <v>185.110371093783</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T29" t="n">
-        <v>218.5027741872469</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U29" t="n">
-        <v>251.261713209344</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H30" t="n">
-        <v>106.8135385761191</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I30" t="n">
-        <v>70.06785926650942</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>65.30202283188841</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S30" t="n">
-        <v>161.2554824245925</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T30" t="n">
-        <v>197.9019079401046</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9044481187107</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.5203236207538</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H31" t="n">
-        <v>158.0426151303904</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I31" t="n">
-        <v>141.296573287914</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J31" t="n">
-        <v>60.08381946093508</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>46.7510432516944</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R31" t="n">
-        <v>156.1309979345465</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S31" t="n">
-        <v>215.8143521353329</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T31" t="n">
-        <v>225.9346058217241</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.2534912839793</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H32" t="n">
-        <v>328.729209150943</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I32" t="n">
-        <v>170.0248242437727</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>83.95940437331049</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S32" t="n">
-        <v>185.110371093783</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T32" t="n">
-        <v>218.5027741872469</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U32" t="n">
-        <v>251.261713209344</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H33" t="n">
-        <v>106.8135385761191</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I33" t="n">
-        <v>70.06785926650942</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>65.30202283188841</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S33" t="n">
-        <v>161.2554824245925</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T33" t="n">
-        <v>197.9019079401046</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9044481187107</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.5203236207538</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H34" t="n">
-        <v>158.0426151303904</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I34" t="n">
-        <v>141.296573287914</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J34" t="n">
-        <v>60.08381946093508</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>46.7510432516944</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R34" t="n">
-        <v>156.1309979345465</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S34" t="n">
-        <v>215.8143521353329</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T34" t="n">
-        <v>225.9346058217241</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.2534912839793</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H35" t="n">
-        <v>328.729209150943</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I35" t="n">
-        <v>170.0248242437727</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>83.95940437331049</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S35" t="n">
-        <v>185.110371093783</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T35" t="n">
-        <v>218.5027741872469</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U35" t="n">
-        <v>251.261713209344</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H36" t="n">
-        <v>106.8135385761191</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I36" t="n">
-        <v>70.06785926650942</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>65.30202283188841</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S36" t="n">
-        <v>161.2554824245925</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T36" t="n">
-        <v>197.9019079401046</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9044481187107</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.5203236207538</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H37" t="n">
-        <v>158.0426151303904</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I37" t="n">
-        <v>141.296573287914</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J37" t="n">
-        <v>60.08381946093508</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>46.7510432516944</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R37" t="n">
-        <v>156.1309979345465</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S37" t="n">
-        <v>215.8143521353329</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T37" t="n">
-        <v>225.9346058217241</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.2534912839793</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H38" t="n">
-        <v>328.729209150943</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I38" t="n">
-        <v>170.0248242437727</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>83.95940437331049</v>
+        <v>74.95115227296736</v>
       </c>
       <c r="S38" t="n">
-        <v>185.110371093783</v>
+        <v>181.8424978167796</v>
       </c>
       <c r="T38" t="n">
-        <v>218.5027741872469</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U38" t="n">
-        <v>251.261713209344</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H39" t="n">
-        <v>106.8135385761191</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I39" t="n">
-        <v>70.06785926650942</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>65.30202283188841</v>
+        <v>60.53808260908391</v>
       </c>
       <c r="S39" t="n">
-        <v>161.2554824245925</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T39" t="n">
-        <v>197.9019079401046</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9044481187107</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.5203236207538</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H40" t="n">
-        <v>158.0426151303904</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I40" t="n">
-        <v>141.296573287914</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J40" t="n">
-        <v>60.08381946093508</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>46.7510432516944</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R40" t="n">
-        <v>156.1309979345465</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S40" t="n">
-        <v>215.8143521353329</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T40" t="n">
-        <v>225.9346058217241</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.2534912839793</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H41" t="n">
-        <v>328.729209150943</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I41" t="n">
-        <v>170.0248242437727</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>83.95940437331049</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S41" t="n">
-        <v>185.110371093783</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T41" t="n">
-        <v>218.5027741872469</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U41" t="n">
-        <v>251.261713209344</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H42" t="n">
-        <v>106.8135385761191</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I42" t="n">
-        <v>70.06785926650942</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>65.30202283188841</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S42" t="n">
-        <v>161.2554824245925</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T42" t="n">
-        <v>197.9019079401046</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9044481187107</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.5203236207538</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H43" t="n">
-        <v>158.0426151303904</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I43" t="n">
-        <v>141.296573287914</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J43" t="n">
-        <v>60.08381946093508</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>46.7510432516944</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R43" t="n">
-        <v>156.1309979345465</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S43" t="n">
-        <v>215.8143521353329</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T43" t="n">
-        <v>225.9346058217241</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.2534912839793</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H44" t="n">
-        <v>328.729209150943</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I44" t="n">
-        <v>170.0248242437727</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>83.95940437331049</v>
+        <v>74.95115227296735</v>
       </c>
       <c r="S44" t="n">
-        <v>185.110371093783</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T44" t="n">
-        <v>218.5027741872469</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U44" t="n">
-        <v>251.261713209344</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H45" t="n">
-        <v>106.8135385761191</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I45" t="n">
-        <v>70.06785926650942</v>
+        <v>67.42608682026646</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>65.30202283188841</v>
+        <v>60.5380826090839</v>
       </c>
       <c r="S45" t="n">
-        <v>161.2554824245925</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T45" t="n">
-        <v>197.9019079401046</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9044481187107</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.5203236207538</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H46" t="n">
-        <v>158.0426151303904</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I46" t="n">
-        <v>141.296573287914</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J46" t="n">
-        <v>60.08381946093508</v>
+        <v>55.53588833985387</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>46.7510432516944</v>
+        <v>41.36451971353327</v>
       </c>
       <c r="R46" t="n">
-        <v>156.1309979345465</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S46" t="n">
-        <v>215.8143521353329</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T46" t="n">
-        <v>225.9346058217241</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>369831.8807884281</v>
+        <v>369569.837869606</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>369831.8807884281</v>
+        <v>369569.837869606</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>369831.8807884281</v>
+        <v>369569.837869606</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>369831.8807884281</v>
+        <v>369569.837869606</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>369831.8807884281</v>
+        <v>369569.837869606</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>369831.8807884281</v>
+        <v>369569.837869606</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>369831.8807884281</v>
+        <v>369569.837869606</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>369831.8807884281</v>
+        <v>369569.837869606</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>369831.8807884281</v>
+        <v>369569.837869606</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>369831.8807884281</v>
+        <v>369569.837869606</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>369831.8807884281</v>
+        <v>369569.837869606</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>369831.8807884281</v>
+        <v>369569.837869606</v>
       </c>
     </row>
   </sheetData>
@@ -26270,40 +26270,40 @@
         <v>53753.70276572321</v>
       </c>
       <c r="E2" t="n">
-        <v>58778.41152462451</v>
+        <v>59383.91788112805</v>
       </c>
       <c r="F2" t="n">
-        <v>58778.41152462453</v>
+        <v>59383.91788112805</v>
       </c>
       <c r="G2" t="n">
-        <v>58778.41152462453</v>
+        <v>59383.91788112805</v>
       </c>
       <c r="H2" t="n">
-        <v>58778.41152462453</v>
+        <v>59383.91788112805</v>
       </c>
       <c r="I2" t="n">
-        <v>58778.41152462453</v>
+        <v>59383.91788112805</v>
       </c>
       <c r="J2" t="n">
-        <v>58778.41152462453</v>
+        <v>59383.91788112805</v>
       </c>
       <c r="K2" t="n">
-        <v>58778.41152462453</v>
+        <v>59383.91788112804</v>
       </c>
       <c r="L2" t="n">
-        <v>58778.41152462453</v>
+        <v>59383.91788112805</v>
       </c>
       <c r="M2" t="n">
-        <v>58778.41152462453</v>
+        <v>59383.91788112804</v>
       </c>
       <c r="N2" t="n">
-        <v>58778.41152462453</v>
+        <v>59383.91788112804</v>
       </c>
       <c r="O2" t="n">
-        <v>58778.41152462453</v>
+        <v>59383.91788112804</v>
       </c>
       <c r="P2" t="n">
-        <v>58778.41152462453</v>
+        <v>59383.91788112804</v>
       </c>
     </row>
     <row r="3">
@@ -26322,7 +26322,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>209688.183</v>
+        <v>238347.4490273461</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48378.33248915087</v>
+        <v>50994.57005901547</v>
       </c>
       <c r="C4" t="n">
-        <v>48378.33248915088</v>
+        <v>50994.57005901547</v>
       </c>
       <c r="D4" t="n">
-        <v>48378.33248915087</v>
+        <v>50994.57005901547</v>
       </c>
       <c r="E4" t="n">
-        <v>17161.41164068085</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="F4" t="n">
-        <v>17161.41164068085</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="G4" t="n">
-        <v>17161.41164068085</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="H4" t="n">
-        <v>17161.41164068085</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="I4" t="n">
-        <v>17161.41164068085</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="J4" t="n">
-        <v>17161.41164068085</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="K4" t="n">
-        <v>17161.41164068085</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="L4" t="n">
-        <v>17161.41164068085</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="M4" t="n">
-        <v>17161.41164068085</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="N4" t="n">
-        <v>17161.41164068085</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="O4" t="n">
-        <v>17161.41164068085</v>
+        <v>13983.75656052792</v>
       </c>
       <c r="P4" t="n">
-        <v>17161.41164068085</v>
+        <v>13983.75656052792</v>
       </c>
     </row>
     <row r="5">
@@ -26426,40 +26426,40 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>5689.799999999999</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="F5" t="n">
-        <v>5689.799999999999</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="G5" t="n">
-        <v>5689.799999999999</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="H5" t="n">
-        <v>5689.799999999999</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="I5" t="n">
-        <v>5689.799999999999</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="J5" t="n">
-        <v>5689.799999999999</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="K5" t="n">
-        <v>5689.799999999999</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="L5" t="n">
-        <v>5689.799999999999</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="M5" t="n">
-        <v>5689.799999999999</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="N5" t="n">
-        <v>5689.799999999999</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="O5" t="n">
-        <v>5689.799999999999</v>
+        <v>6467.457040608691</v>
       </c>
       <c r="P5" t="n">
-        <v>5689.799999999999</v>
+        <v>6467.457040608691</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-28252.22972342766</v>
+        <v>-30868.46729329226</v>
       </c>
       <c r="C6" t="n">
-        <v>-28252.22972342767</v>
+        <v>-30868.46729329226</v>
       </c>
       <c r="D6" t="n">
-        <v>-28252.22972342766</v>
+        <v>-30868.46729329226</v>
       </c>
       <c r="E6" t="n">
-        <v>-173760.9831160563</v>
+        <v>-199414.7447473546</v>
       </c>
       <c r="F6" t="n">
-        <v>35927.19988394367</v>
+        <v>38932.70427999144</v>
       </c>
       <c r="G6" t="n">
-        <v>35927.19988394367</v>
+        <v>38932.70427999144</v>
       </c>
       <c r="H6" t="n">
-        <v>35927.19988394367</v>
+        <v>38932.70427999144</v>
       </c>
       <c r="I6" t="n">
-        <v>35927.19988394367</v>
+        <v>38932.70427999144</v>
       </c>
       <c r="J6" t="n">
-        <v>35927.19988394367</v>
+        <v>38932.70427999144</v>
       </c>
       <c r="K6" t="n">
-        <v>35927.19988394367</v>
+        <v>38932.70427999143</v>
       </c>
       <c r="L6" t="n">
-        <v>35927.19988394367</v>
+        <v>38932.70427999144</v>
       </c>
       <c r="M6" t="n">
-        <v>35927.19988394369</v>
+        <v>38932.70427999143</v>
       </c>
       <c r="N6" t="n">
-        <v>35927.19988394369</v>
+        <v>38932.70427999143</v>
       </c>
       <c r="O6" t="n">
-        <v>35927.19988394367</v>
+        <v>38932.70427999143</v>
       </c>
       <c r="P6" t="n">
-        <v>35927.19988394367</v>
+        <v>38932.70427999143</v>
       </c>
     </row>
   </sheetData>
@@ -26684,40 +26684,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>260.9999999999999</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="F3" t="n">
-        <v>260.9999999999999</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="G3" t="n">
-        <v>260.9999999999999</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="H3" t="n">
-        <v>260.9999999999999</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="I3" t="n">
-        <v>260.9999999999999</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="J3" t="n">
-        <v>260.9999999999999</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="K3" t="n">
-        <v>260.9999999999999</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="L3" t="n">
-        <v>260.9999999999999</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="M3" t="n">
-        <v>260.9999999999999</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="N3" t="n">
-        <v>260.9999999999999</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="O3" t="n">
-        <v>260.9999999999999</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="P3" t="n">
-        <v>260.9999999999999</v>
+        <v>296.6723413123253</v>
       </c>
     </row>
     <row r="4">
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>261</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,46 +26947,46 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.049246231155778</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H11" t="n">
-        <v>10.74559296482411</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I11" t="n">
-        <v>40.45106532663317</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J11" t="n">
-        <v>89.05346231155778</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K11" t="n">
-        <v>133.4680552763819</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L11" t="n">
-        <v>165.5789246231156</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M11" t="n">
-        <v>184.2384572864322</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N11" t="n">
-        <v>187.2196281407035</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O11" t="n">
-        <v>176.7861859296482</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P11" t="n">
-        <v>150.8829195979899</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.3067889447236</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R11" t="n">
-        <v>65.90971356783919</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S11" t="n">
-        <v>23.90969849246232</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T11" t="n">
-        <v>4.59307537688442</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08393969849246222</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,22 +31749,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5613962264150942</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H12" t="n">
-        <v>5.421905660377359</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I12" t="n">
-        <v>19.32877358490566</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J12" t="n">
-        <v>53.0396320754717</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K12" t="n">
-        <v>90.65317924528301</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L12" t="n">
-        <v>121.8943867924528</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
         <v>142.1340339220183</v>
@@ -31773,25 +31773,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>133.5704433962264</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>107.2020566037736</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q12" t="n">
-        <v>71.66173584905661</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R12" t="n">
-        <v>34.85581132075473</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S12" t="n">
-        <v>10.42768867924527</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T12" t="n">
-        <v>2.26282075471698</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.470655737704918</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H13" t="n">
-        <v>4.184557377049182</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I13" t="n">
-        <v>14.15390163934426</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J13" t="n">
-        <v>33.2753606557377</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K13" t="n">
-        <v>54.68163934426227</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L13" t="n">
-        <v>69.97367213114754</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M13" t="n">
-        <v>73.77742622950817</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N13" t="n">
-        <v>72.02316393442626</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O13" t="n">
-        <v>66.52504918032787</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P13" t="n">
-        <v>56.92367213114751</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q13" t="n">
-        <v>39.41099999999999</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R13" t="n">
-        <v>21.16239344262294</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S13" t="n">
-        <v>8.202245901639339</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T13" t="n">
-        <v>2.010983606557376</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.049246231155778</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H14" t="n">
-        <v>10.74559296482411</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I14" t="n">
-        <v>40.45106532663316</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J14" t="n">
-        <v>89.05346231155778</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K14" t="n">
-        <v>133.4680552763819</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L14" t="n">
-        <v>165.5789246231156</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M14" t="n">
-        <v>184.2384572864321</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N14" t="n">
-        <v>187.2196281407035</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O14" t="n">
-        <v>176.7861859296482</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P14" t="n">
-        <v>150.8829195979899</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.3067889447236</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R14" t="n">
-        <v>65.90971356783919</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S14" t="n">
-        <v>23.90969849246231</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T14" t="n">
-        <v>4.59307537688442</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08393969849246222</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,22 +31986,22 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5613962264150942</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H15" t="n">
-        <v>5.421905660377358</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I15" t="n">
-        <v>19.32877358490566</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J15" t="n">
-        <v>53.03963207547169</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K15" t="n">
-        <v>90.65317924528301</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L15" t="n">
-        <v>121.8943867924528</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
         <v>142.1340339220183</v>
@@ -32010,25 +32010,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>133.5704433962264</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>107.2020566037736</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q15" t="n">
-        <v>71.6617358490566</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R15" t="n">
-        <v>34.85581132075473</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S15" t="n">
-        <v>10.42768867924527</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T15" t="n">
-        <v>2.26282075471698</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03693396226415095</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4706557377049179</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H16" t="n">
-        <v>4.184557377049182</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I16" t="n">
-        <v>14.15390163934426</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J16" t="n">
-        <v>33.27536065573769</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K16" t="n">
-        <v>54.68163934426227</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L16" t="n">
-        <v>69.97367213114752</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M16" t="n">
-        <v>73.77742622950817</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N16" t="n">
-        <v>72.02316393442625</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O16" t="n">
-        <v>66.52504918032787</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P16" t="n">
-        <v>56.9236721311475</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q16" t="n">
-        <v>39.41099999999999</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R16" t="n">
-        <v>21.16239344262294</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S16" t="n">
-        <v>8.202245901639339</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T16" t="n">
-        <v>2.010983606557376</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U16" t="n">
-        <v>0.025672131147541</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.049246231155778</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H17" t="n">
-        <v>10.74559296482411</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I17" t="n">
-        <v>40.45106532663316</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J17" t="n">
-        <v>89.05346231155778</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K17" t="n">
-        <v>133.4680552763819</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L17" t="n">
-        <v>165.5789246231156</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M17" t="n">
-        <v>184.2384572864321</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N17" t="n">
-        <v>187.2196281407035</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O17" t="n">
-        <v>176.7861859296482</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P17" t="n">
-        <v>150.8829195979899</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.3067889447236</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R17" t="n">
-        <v>65.90971356783919</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S17" t="n">
-        <v>23.90969849246231</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T17" t="n">
-        <v>4.59307537688442</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08393969849246222</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,22 +32223,22 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5613962264150942</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H18" t="n">
-        <v>5.421905660377358</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I18" t="n">
-        <v>19.32877358490566</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J18" t="n">
-        <v>53.03963207547169</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K18" t="n">
-        <v>90.65317924528301</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L18" t="n">
-        <v>121.8943867924528</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
@@ -32247,25 +32247,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>133.5704433962264</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>107.2020566037736</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q18" t="n">
-        <v>71.6617358490566</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R18" t="n">
-        <v>34.85581132075473</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S18" t="n">
-        <v>10.42768867924527</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T18" t="n">
-        <v>2.26282075471698</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U18" t="n">
-        <v>0.03693396226415095</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4706557377049179</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H19" t="n">
-        <v>4.184557377049182</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I19" t="n">
-        <v>14.15390163934426</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J19" t="n">
-        <v>33.27536065573769</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K19" t="n">
-        <v>54.68163934426227</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L19" t="n">
-        <v>69.97367213114752</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M19" t="n">
-        <v>73.77742622950817</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N19" t="n">
-        <v>72.02316393442625</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O19" t="n">
-        <v>66.52504918032787</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P19" t="n">
-        <v>56.9236721311475</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q19" t="n">
-        <v>39.41099999999999</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R19" t="n">
-        <v>21.16239344262294</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S19" t="n">
-        <v>8.202245901639339</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T19" t="n">
-        <v>2.010983606557376</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U19" t="n">
-        <v>0.025672131147541</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.049246231155778</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H20" t="n">
-        <v>10.74559296482411</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I20" t="n">
-        <v>40.45106532663316</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J20" t="n">
-        <v>89.05346231155778</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K20" t="n">
-        <v>133.4680552763819</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L20" t="n">
-        <v>165.5789246231156</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M20" t="n">
-        <v>184.2384572864321</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N20" t="n">
-        <v>187.2196281407035</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O20" t="n">
-        <v>176.7861859296482</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P20" t="n">
-        <v>150.8829195979899</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.3067889447236</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R20" t="n">
-        <v>65.90971356783919</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S20" t="n">
-        <v>23.90969849246231</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T20" t="n">
-        <v>4.59307537688442</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08393969849246222</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,22 +32460,22 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5613962264150942</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H21" t="n">
-        <v>5.421905660377358</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I21" t="n">
-        <v>19.32877358490566</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J21" t="n">
-        <v>53.03963207547169</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K21" t="n">
-        <v>90.65317924528301</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L21" t="n">
-        <v>121.8943867924528</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
         <v>142.1340339220183</v>
@@ -32484,25 +32484,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>133.5704433962264</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>107.2020566037736</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q21" t="n">
-        <v>71.6617358490566</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R21" t="n">
-        <v>34.85581132075473</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S21" t="n">
-        <v>10.42768867924527</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T21" t="n">
-        <v>2.26282075471698</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U21" t="n">
-        <v>0.03693396226415095</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4706557377049179</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H22" t="n">
-        <v>4.184557377049182</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I22" t="n">
-        <v>14.15390163934426</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J22" t="n">
-        <v>33.27536065573769</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K22" t="n">
-        <v>54.68163934426227</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L22" t="n">
-        <v>69.97367213114752</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M22" t="n">
-        <v>73.77742622950817</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N22" t="n">
-        <v>72.02316393442625</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O22" t="n">
-        <v>66.52504918032787</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P22" t="n">
-        <v>56.9236721311475</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q22" t="n">
-        <v>39.41099999999999</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R22" t="n">
-        <v>21.16239344262294</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S22" t="n">
-        <v>8.202245901639339</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T22" t="n">
-        <v>2.010983606557376</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U22" t="n">
-        <v>0.025672131147541</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.049246231155778</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H23" t="n">
-        <v>10.74559296482411</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I23" t="n">
-        <v>40.45106532663316</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J23" t="n">
-        <v>89.05346231155778</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K23" t="n">
-        <v>133.4680552763819</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L23" t="n">
-        <v>165.5789246231156</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M23" t="n">
-        <v>184.2384572864321</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N23" t="n">
-        <v>187.2196281407035</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O23" t="n">
-        <v>176.7861859296482</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P23" t="n">
-        <v>150.8829195979899</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.3067889447236</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R23" t="n">
-        <v>65.90971356783919</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S23" t="n">
-        <v>23.90969849246231</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T23" t="n">
-        <v>4.59307537688442</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08393969849246222</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,22 +32697,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5613962264150942</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H24" t="n">
-        <v>5.421905660377358</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I24" t="n">
-        <v>19.32877358490566</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J24" t="n">
-        <v>53.03963207547169</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K24" t="n">
-        <v>90.65317924528301</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L24" t="n">
-        <v>121.8943867924528</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
         <v>142.1340339220183</v>
@@ -32721,25 +32721,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>133.5704433962264</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>107.2020566037736</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q24" t="n">
-        <v>71.6617358490566</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R24" t="n">
-        <v>34.85581132075473</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S24" t="n">
-        <v>10.42768867924527</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T24" t="n">
-        <v>2.26282075471698</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03693396226415095</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4706557377049179</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H25" t="n">
-        <v>4.184557377049182</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I25" t="n">
-        <v>14.15390163934426</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J25" t="n">
-        <v>33.27536065573769</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K25" t="n">
-        <v>54.68163934426227</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L25" t="n">
-        <v>69.97367213114752</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M25" t="n">
-        <v>73.77742622950817</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N25" t="n">
-        <v>72.02316393442625</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O25" t="n">
-        <v>66.52504918032787</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P25" t="n">
-        <v>56.9236721311475</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q25" t="n">
-        <v>39.41099999999999</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R25" t="n">
-        <v>21.16239344262294</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S25" t="n">
-        <v>8.202245901639339</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T25" t="n">
-        <v>2.010983606557376</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U25" t="n">
-        <v>0.025672131147541</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.049246231155778</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H26" t="n">
-        <v>10.74559296482411</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I26" t="n">
-        <v>40.45106532663316</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J26" t="n">
-        <v>89.05346231155778</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K26" t="n">
-        <v>133.4680552763819</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L26" t="n">
-        <v>165.5789246231156</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M26" t="n">
-        <v>184.2384572864321</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N26" t="n">
-        <v>187.2196281407035</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O26" t="n">
-        <v>176.7861859296482</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P26" t="n">
-        <v>150.8829195979899</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.3067889447236</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R26" t="n">
-        <v>65.90971356783919</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S26" t="n">
-        <v>23.90969849246231</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T26" t="n">
-        <v>4.59307537688442</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U26" t="n">
-        <v>0.08393969849246222</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,22 +32934,22 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5613962264150942</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H27" t="n">
-        <v>5.421905660377358</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I27" t="n">
-        <v>19.32877358490566</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J27" t="n">
-        <v>53.03963207547169</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K27" t="n">
-        <v>90.65317924528301</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L27" t="n">
-        <v>121.8943867924528</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
@@ -32958,25 +32958,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>133.5704433962264</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>107.2020566037736</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q27" t="n">
-        <v>71.6617358490566</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R27" t="n">
-        <v>34.85581132075473</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S27" t="n">
-        <v>10.42768867924527</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T27" t="n">
-        <v>2.26282075471698</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U27" t="n">
-        <v>0.03693396226415095</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4706557377049179</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H28" t="n">
-        <v>4.184557377049182</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I28" t="n">
-        <v>14.15390163934426</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J28" t="n">
-        <v>33.27536065573769</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K28" t="n">
-        <v>54.68163934426227</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L28" t="n">
-        <v>69.97367213114752</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M28" t="n">
-        <v>73.77742622950817</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N28" t="n">
-        <v>72.02316393442625</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O28" t="n">
-        <v>66.52504918032787</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P28" t="n">
-        <v>56.9236721311475</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q28" t="n">
-        <v>39.41099999999999</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R28" t="n">
-        <v>21.16239344262294</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S28" t="n">
-        <v>8.202245901639339</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T28" t="n">
-        <v>2.010983606557376</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U28" t="n">
-        <v>0.025672131147541</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.049246231155778</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H29" t="n">
-        <v>10.74559296482411</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I29" t="n">
-        <v>40.45106532663316</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J29" t="n">
-        <v>89.05346231155778</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K29" t="n">
-        <v>133.4680552763819</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L29" t="n">
-        <v>165.5789246231156</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M29" t="n">
-        <v>184.2384572864321</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N29" t="n">
-        <v>187.2196281407035</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O29" t="n">
-        <v>176.7861859296482</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P29" t="n">
-        <v>150.8829195979899</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.3067889447236</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R29" t="n">
-        <v>65.90971356783919</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S29" t="n">
-        <v>23.90969849246231</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T29" t="n">
-        <v>4.59307537688442</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U29" t="n">
-        <v>0.08393969849246222</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,22 +33171,22 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5613962264150942</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H30" t="n">
-        <v>5.421905660377358</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I30" t="n">
-        <v>19.32877358490566</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J30" t="n">
-        <v>53.03963207547169</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K30" t="n">
-        <v>90.65317924528301</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L30" t="n">
-        <v>121.8943867924528</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
         <v>142.1340339220183</v>
@@ -33195,25 +33195,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>133.5704433962264</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>107.2020566037736</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q30" t="n">
-        <v>71.6617358490566</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R30" t="n">
-        <v>34.85581132075473</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S30" t="n">
-        <v>10.42768867924527</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T30" t="n">
-        <v>2.26282075471698</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U30" t="n">
-        <v>0.03693396226415095</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4706557377049179</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H31" t="n">
-        <v>4.184557377049182</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I31" t="n">
-        <v>14.15390163934426</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J31" t="n">
-        <v>33.27536065573769</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K31" t="n">
-        <v>54.68163934426227</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L31" t="n">
-        <v>69.97367213114752</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M31" t="n">
-        <v>73.77742622950817</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N31" t="n">
-        <v>72.02316393442625</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O31" t="n">
-        <v>66.52504918032787</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P31" t="n">
-        <v>56.9236721311475</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q31" t="n">
-        <v>39.41099999999999</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R31" t="n">
-        <v>21.16239344262294</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S31" t="n">
-        <v>8.202245901639339</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T31" t="n">
-        <v>2.010983606557376</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U31" t="n">
-        <v>0.025672131147541</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.049246231155778</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H32" t="n">
-        <v>10.74559296482411</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I32" t="n">
-        <v>40.45106532663316</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J32" t="n">
-        <v>89.05346231155778</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K32" t="n">
-        <v>133.4680552763819</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L32" t="n">
-        <v>165.5789246231156</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M32" t="n">
-        <v>184.2384572864321</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N32" t="n">
-        <v>187.2196281407035</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O32" t="n">
-        <v>176.7861859296482</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P32" t="n">
-        <v>150.8829195979899</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q32" t="n">
-        <v>113.3067889447236</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R32" t="n">
-        <v>65.90971356783919</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S32" t="n">
-        <v>23.90969849246231</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T32" t="n">
-        <v>4.59307537688442</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U32" t="n">
-        <v>0.08393969849246222</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,22 +33408,22 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5613962264150942</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H33" t="n">
-        <v>5.421905660377358</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I33" t="n">
-        <v>19.32877358490566</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J33" t="n">
-        <v>53.03963207547169</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K33" t="n">
-        <v>90.65317924528301</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L33" t="n">
-        <v>121.8943867924528</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
         <v>142.1340339220183</v>
@@ -33432,25 +33432,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>133.5704433962264</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>107.2020566037736</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q33" t="n">
-        <v>71.6617358490566</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R33" t="n">
-        <v>34.85581132075473</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S33" t="n">
-        <v>10.42768867924527</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T33" t="n">
-        <v>2.26282075471698</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U33" t="n">
-        <v>0.03693396226415095</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4706557377049179</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H34" t="n">
-        <v>4.184557377049182</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I34" t="n">
-        <v>14.15390163934426</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J34" t="n">
-        <v>33.27536065573769</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K34" t="n">
-        <v>54.68163934426227</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L34" t="n">
-        <v>69.97367213114752</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M34" t="n">
-        <v>73.77742622950817</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N34" t="n">
-        <v>72.02316393442625</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O34" t="n">
-        <v>66.52504918032787</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P34" t="n">
-        <v>56.9236721311475</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q34" t="n">
-        <v>39.41099999999999</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R34" t="n">
-        <v>21.16239344262294</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S34" t="n">
-        <v>8.202245901639339</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T34" t="n">
-        <v>2.010983606557376</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U34" t="n">
-        <v>0.025672131147541</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.049246231155778</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H35" t="n">
-        <v>10.74559296482411</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I35" t="n">
-        <v>40.45106532663316</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J35" t="n">
-        <v>89.05346231155778</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K35" t="n">
-        <v>133.4680552763819</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L35" t="n">
-        <v>165.5789246231156</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M35" t="n">
-        <v>184.2384572864321</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N35" t="n">
-        <v>187.2196281407035</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O35" t="n">
-        <v>176.7861859296482</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P35" t="n">
-        <v>150.8829195979899</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q35" t="n">
-        <v>113.3067889447236</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R35" t="n">
-        <v>65.90971356783919</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S35" t="n">
-        <v>23.90969849246231</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T35" t="n">
-        <v>4.59307537688442</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U35" t="n">
-        <v>0.08393969849246222</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,22 +33645,22 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5613962264150942</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H36" t="n">
-        <v>5.421905660377358</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I36" t="n">
-        <v>19.32877358490566</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J36" t="n">
-        <v>53.03963207547169</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K36" t="n">
-        <v>90.65317924528301</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L36" t="n">
-        <v>121.8943867924528</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
         <v>142.1340339220183</v>
@@ -33669,25 +33669,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>133.5704433962264</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>107.2020566037736</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q36" t="n">
-        <v>71.6617358490566</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R36" t="n">
-        <v>34.85581132075473</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S36" t="n">
-        <v>10.42768867924527</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T36" t="n">
-        <v>2.26282075471698</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U36" t="n">
-        <v>0.03693396226415095</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4706557377049179</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H37" t="n">
-        <v>4.184557377049182</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I37" t="n">
-        <v>14.15390163934426</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J37" t="n">
-        <v>33.27536065573769</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K37" t="n">
-        <v>54.68163934426227</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L37" t="n">
-        <v>69.97367213114752</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M37" t="n">
-        <v>73.77742622950817</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N37" t="n">
-        <v>72.02316393442625</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O37" t="n">
-        <v>66.52504918032787</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P37" t="n">
-        <v>56.9236721311475</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q37" t="n">
-        <v>39.41099999999999</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R37" t="n">
-        <v>21.16239344262294</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S37" t="n">
-        <v>8.202245901639339</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T37" t="n">
-        <v>2.010983606557376</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U37" t="n">
-        <v>0.025672131147541</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.049246231155778</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H38" t="n">
-        <v>10.74559296482411</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I38" t="n">
-        <v>40.45106532663316</v>
+        <v>45.97974045605395</v>
       </c>
       <c r="J38" t="n">
-        <v>89.05346231155778</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K38" t="n">
-        <v>133.4680552763819</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L38" t="n">
-        <v>165.5789246231156</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M38" t="n">
-        <v>184.2384572864321</v>
+        <v>209.4193658350063</v>
       </c>
       <c r="N38" t="n">
-        <v>187.2196281407035</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O38" t="n">
-        <v>176.7861859296482</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P38" t="n">
-        <v>150.8829195979899</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q38" t="n">
-        <v>113.3067889447236</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R38" t="n">
-        <v>65.90971356783919</v>
+        <v>74.91796566818232</v>
       </c>
       <c r="S38" t="n">
-        <v>23.90969849246231</v>
+        <v>27.17757176946578</v>
       </c>
       <c r="T38" t="n">
-        <v>4.59307537688442</v>
+        <v>5.220836880782727</v>
       </c>
       <c r="U38" t="n">
-        <v>0.08393969849246222</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,22 +33882,22 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5613962264150942</v>
+        <v>0.638125413388775</v>
       </c>
       <c r="H39" t="n">
-        <v>5.421905660377358</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I39" t="n">
-        <v>19.32877358490566</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J39" t="n">
-        <v>53.03963207547169</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K39" t="n">
-        <v>90.65317924528301</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L39" t="n">
-        <v>121.8943867924528</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
         <v>142.1340339220183</v>
@@ -33906,25 +33906,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>133.5704433962264</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>107.2020566037736</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q39" t="n">
-        <v>71.6617358490566</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R39" t="n">
-        <v>34.85581132075473</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S39" t="n">
-        <v>10.42768867924527</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T39" t="n">
-        <v>2.26282075471698</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U39" t="n">
-        <v>0.03693396226415095</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4706557377049179</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H40" t="n">
-        <v>4.184557377049182</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I40" t="n">
-        <v>14.15390163934426</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J40" t="n">
-        <v>33.27536065573769</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K40" t="n">
-        <v>54.68163934426227</v>
+        <v>62.15528724543468</v>
       </c>
       <c r="L40" t="n">
-        <v>69.97367213114752</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M40" t="n">
-        <v>73.77742622950817</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N40" t="n">
-        <v>72.02316393442625</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O40" t="n">
-        <v>66.52504918032787</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P40" t="n">
-        <v>56.9236721311475</v>
+        <v>64.70375129211759</v>
       </c>
       <c r="Q40" t="n">
-        <v>39.41099999999999</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R40" t="n">
-        <v>21.16239344262294</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S40" t="n">
-        <v>8.202245901639339</v>
+        <v>9.3232930868152</v>
       </c>
       <c r="T40" t="n">
-        <v>2.010983606557376</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U40" t="n">
-        <v>0.025672131147541</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.049246231155778</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H41" t="n">
-        <v>10.74559296482411</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I41" t="n">
-        <v>40.45106532663316</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J41" t="n">
-        <v>89.05346231155778</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K41" t="n">
-        <v>133.4680552763819</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L41" t="n">
-        <v>165.5789246231156</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M41" t="n">
-        <v>184.2384572864321</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N41" t="n">
-        <v>187.2196281407035</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O41" t="n">
-        <v>176.7861859296482</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P41" t="n">
-        <v>150.8829195979899</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.3067889447236</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R41" t="n">
-        <v>65.90971356783919</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S41" t="n">
-        <v>23.90969849246231</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T41" t="n">
-        <v>4.59307537688442</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U41" t="n">
-        <v>0.08393969849246222</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,22 +34119,22 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5613962264150942</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H42" t="n">
-        <v>5.421905660377358</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I42" t="n">
-        <v>19.32877358490566</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J42" t="n">
-        <v>53.03963207547169</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K42" t="n">
-        <v>90.65317924528301</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L42" t="n">
-        <v>121.8943867924528</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
         <v>142.1340339220183</v>
@@ -34143,25 +34143,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>133.5704433962264</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>107.2020566037736</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q42" t="n">
-        <v>71.6617358490566</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R42" t="n">
-        <v>34.85581132075473</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S42" t="n">
-        <v>10.42768867924527</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T42" t="n">
-        <v>2.26282075471698</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U42" t="n">
-        <v>0.03693396226415095</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4706557377049179</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H43" t="n">
-        <v>4.184557377049182</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I43" t="n">
-        <v>14.15390163934426</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J43" t="n">
-        <v>33.27536065573769</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K43" t="n">
-        <v>54.68163934426227</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L43" t="n">
-        <v>69.97367213114752</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M43" t="n">
-        <v>73.77742622950817</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N43" t="n">
-        <v>72.02316393442625</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O43" t="n">
-        <v>66.52504918032787</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P43" t="n">
-        <v>56.9236721311475</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q43" t="n">
-        <v>39.41099999999999</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R43" t="n">
-        <v>21.16239344262294</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S43" t="n">
-        <v>8.202245901639339</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T43" t="n">
-        <v>2.010983606557376</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U43" t="n">
-        <v>0.025672131147541</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.049246231155778</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H44" t="n">
-        <v>10.74559296482411</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I44" t="n">
-        <v>40.45106532663316</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J44" t="n">
-        <v>89.05346231155778</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K44" t="n">
-        <v>133.4680552763819</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L44" t="n">
-        <v>165.5789246231156</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M44" t="n">
-        <v>184.2384572864321</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N44" t="n">
-        <v>187.2196281407035</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O44" t="n">
-        <v>176.7861859296482</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P44" t="n">
-        <v>150.8829195979899</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q44" t="n">
-        <v>113.3067889447236</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R44" t="n">
-        <v>65.90971356783919</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S44" t="n">
-        <v>23.90969849246231</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T44" t="n">
-        <v>4.59307537688442</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08393969849246222</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,22 +34356,22 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5613962264150942</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H45" t="n">
-        <v>5.421905660377358</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I45" t="n">
-        <v>19.32877358490566</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J45" t="n">
-        <v>53.03963207547169</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K45" t="n">
-        <v>90.65317924528301</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L45" t="n">
-        <v>121.8943867924528</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M45" t="n">
         <v>142.1340339220183</v>
@@ -34380,25 +34380,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O45" t="n">
-        <v>133.5704433962264</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>107.2020566037736</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q45" t="n">
-        <v>71.6617358490566</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R45" t="n">
-        <v>34.85581132075473</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S45" t="n">
-        <v>10.42768867924527</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T45" t="n">
-        <v>2.26282075471698</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U45" t="n">
-        <v>0.03693396226415095</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4706557377049179</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H46" t="n">
-        <v>4.184557377049182</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I46" t="n">
-        <v>14.15390163934426</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J46" t="n">
-        <v>33.27536065573769</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K46" t="n">
-        <v>54.68163934426227</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L46" t="n">
-        <v>69.97367213114752</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M46" t="n">
-        <v>73.77742622950817</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N46" t="n">
-        <v>72.02316393442625</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O46" t="n">
-        <v>66.52504918032787</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P46" t="n">
-        <v>56.9236721311475</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q46" t="n">
-        <v>39.41099999999999</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R46" t="n">
-        <v>21.16239344262294</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S46" t="n">
-        <v>8.202245901639339</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T46" t="n">
-        <v>2.010983606557376</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U46" t="n">
-        <v>0.025672131147541</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
